--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/KANSAS_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/KANSAS_2015.xlsx
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C155">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C245">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C605">
